--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -20,8 +20,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S160: Hands on real-time Docker
+  Gus U. Green
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S160: Hands on real-time Docker
+  Gus U. Green
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C69" authorId="0">
+      <text>
+        <t>S160: Hands on real-time Docker
+  Gus U. Green
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S160: Hands on real-time Docker
+  Gus U. Green
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12160" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12194" uniqueCount="818">
   <si>
     <t>Conference name</t>
   </si>
@@ -2787,6 +2855,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -2933,26 +3004,60 @@
       <c r="A3" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>817</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -2962,6 +3067,7 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -31664,6 +31770,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -33013,11 +33122,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -41664,11 +41777,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -41815,26 +41932,60 @@
       <c r="A3" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -41844,11 +41995,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12620" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12621" uniqueCount="861">
   <si>
     <t>Conference name</t>
   </si>
@@ -930,7 +930,7 @@
     <t>Sector tags</t>
   </si>
   <si>
-    <t>Audience type</t>
+    <t>Audience types</t>
   </si>
   <si>
     <t>Audience level</t>
@@ -2686,6 +2686,9 @@
   </si>
   <si>
     <t>Usable sessions</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>S146: Tuning IOT-driven Weld
@@ -2702,6 +2705,9 @@
   </si>
   <si>
     <t>Sector tag</t>
+  </si>
+  <si>
+    <t>Audience type</t>
   </si>
   <si>
     <t>1</t>
@@ -3300,7 +3306,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -3458,7 +3464,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>265</v>
+        <v>857</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -3523,7 +3529,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -3735,13 +3741,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -3894,7 +3900,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -3959,7 +3965,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -33511,6 +33517,24 @@
       </c>
       <c r="E5" s="2" t="n">
         <v>192.0</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>216.0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>360.0</v>
       </c>
     </row>
   </sheetData>
@@ -33693,7 +33717,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -34967,7 +34991,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -38985,7 +39009,7 @@
         <v>65</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>65</v>
@@ -43622,7 +43646,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -43687,7 +43711,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -43746,7 +43770,7 @@
         <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>65</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -4537,7 +4537,7 @@
       <c r="C3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -4546,7 +4546,7 @@
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -4555,7 +4555,7 @@
       <c r="I3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -4564,7 +4564,7 @@
       <c r="L3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -4573,7 +4573,7 @@
       <c r="O3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q3" s="2" t="s">
@@ -4582,7 +4582,7 @@
       <c r="R3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T3" s="2" t="s">
@@ -4602,7 +4602,7 @@
       <c r="C4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -4611,7 +4611,7 @@
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -4620,7 +4620,7 @@
       <c r="I4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -4629,7 +4629,7 @@
       <c r="L4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N4" s="2" t="s">
@@ -4638,7 +4638,7 @@
       <c r="O4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q4" s="2" t="s">
@@ -4647,7 +4647,7 @@
       <c r="R4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T4" s="2" t="s">
@@ -4667,7 +4667,7 @@
       <c r="C5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -4676,7 +4676,7 @@
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -4685,7 +4685,7 @@
       <c r="I5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -4694,7 +4694,7 @@
       <c r="L5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
@@ -4703,7 +4703,7 @@
       <c r="O5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q5" s="2" t="s">
@@ -4712,7 +4712,7 @@
       <c r="R5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T5" s="2" t="s">
@@ -4732,7 +4732,7 @@
       <c r="C6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -4741,7 +4741,7 @@
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -4750,7 +4750,7 @@
       <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -4759,7 +4759,7 @@
       <c r="L6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -4768,7 +4768,7 @@
       <c r="O6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q6" s="2" t="s">
@@ -4777,7 +4777,7 @@
       <c r="R6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="S6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T6" s="2" t="s">
@@ -4800,55 +4800,55 @@
       <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="H7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="K7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O7" s="3" t="s">
+      <c r="N7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="3" t="s">
+      <c r="Q7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U7" s="3" t="s">
+      <c r="T7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       <c r="C8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -4871,7 +4871,7 @@
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -4880,7 +4880,7 @@
       <c r="I8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -4889,7 +4889,7 @@
       <c r="L8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
@@ -4898,7 +4898,7 @@
       <c r="O8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q8" s="2" t="s">
@@ -4907,7 +4907,7 @@
       <c r="R8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="S8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T8" s="2" t="s">
@@ -4927,7 +4927,7 @@
       <c r="C9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -4936,7 +4936,7 @@
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -4945,7 +4945,7 @@
       <c r="I9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -4954,7 +4954,7 @@
       <c r="L9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N9" s="2" t="s">
@@ -4963,7 +4963,7 @@
       <c r="O9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q9" s="2" t="s">
@@ -4972,7 +4972,7 @@
       <c r="R9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T9" s="2" t="s">
@@ -4992,7 +4992,7 @@
       <c r="C10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -5001,7 +5001,7 @@
       <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -5010,7 +5010,7 @@
       <c r="I10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -5019,7 +5019,7 @@
       <c r="L10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
@@ -5028,7 +5028,7 @@
       <c r="O10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="P10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q10" s="2" t="s">
@@ -5037,7 +5037,7 @@
       <c r="R10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="S10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T10" s="2" t="s">
@@ -5057,7 +5057,7 @@
       <c r="C11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -5066,7 +5066,7 @@
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -5075,7 +5075,7 @@
       <c r="I11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -5084,7 +5084,7 @@
       <c r="L11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
@@ -5093,7 +5093,7 @@
       <c r="O11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="P11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q11" s="2" t="s">
@@ -5102,7 +5102,7 @@
       <c r="R11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T11" s="2" t="s">
@@ -5125,55 +5125,55 @@
       <c r="D12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="H12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="K12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" s="3" t="s">
+      <c r="N12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R12" s="3" t="s">
+      <c r="Q12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U12" s="3" t="s">
+      <c r="T12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       <c r="C13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -5196,7 +5196,7 @@
       <c r="F13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -5205,7 +5205,7 @@
       <c r="I13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -5214,7 +5214,7 @@
       <c r="L13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="M13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N13" s="2" t="s">
@@ -5223,7 +5223,7 @@
       <c r="O13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="P13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q13" s="2" t="s">
@@ -5232,7 +5232,7 @@
       <c r="R13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S13" s="3" t="s">
+      <c r="S13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T13" s="2" t="s">
@@ -5252,7 +5252,7 @@
       <c r="C14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -5261,7 +5261,7 @@
       <c r="F14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -5270,7 +5270,7 @@
       <c r="I14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -5279,7 +5279,7 @@
       <c r="L14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N14" s="2" t="s">
@@ -5288,7 +5288,7 @@
       <c r="O14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="P14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q14" s="2" t="s">
@@ -5297,7 +5297,7 @@
       <c r="R14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T14" s="2" t="s">
@@ -5317,7 +5317,7 @@
       <c r="C15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -5326,7 +5326,7 @@
       <c r="F15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -5335,7 +5335,7 @@
       <c r="I15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -5344,7 +5344,7 @@
       <c r="L15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N15" s="2" t="s">
@@ -5353,7 +5353,7 @@
       <c r="O15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="P15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q15" s="2" t="s">
@@ -5362,7 +5362,7 @@
       <c r="R15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T15" s="2" t="s">
@@ -5382,7 +5382,7 @@
       <c r="C16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -5391,7 +5391,7 @@
       <c r="F16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -5400,7 +5400,7 @@
       <c r="I16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K16" s="2" t="s">
@@ -5409,7 +5409,7 @@
       <c r="L16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="M16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N16" s="2" t="s">
@@ -5418,7 +5418,7 @@
       <c r="O16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P16" s="3" t="s">
+      <c r="P16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q16" s="2" t="s">
@@ -5427,7 +5427,7 @@
       <c r="R16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S16" s="3" t="s">
+      <c r="S16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T16" s="2" t="s">
@@ -5450,55 +5450,55 @@
       <c r="D17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="E17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="H17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L17" s="3" t="s">
+      <c r="K17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O17" s="3" t="s">
+      <c r="N17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R17" s="3" t="s">
+      <c r="Q17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U17" s="3" t="s">
+      <c r="T17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U17" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       <c r="C18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -5521,7 +5521,7 @@
       <c r="F18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -5530,7 +5530,7 @@
       <c r="I18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K18" s="2" t="s">
@@ -5539,7 +5539,7 @@
       <c r="L18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="M18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N18" s="2" t="s">
@@ -5548,7 +5548,7 @@
       <c r="O18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P18" s="3" t="s">
+      <c r="P18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q18" s="2" t="s">
@@ -5557,7 +5557,7 @@
       <c r="R18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S18" s="3" t="s">
+      <c r="S18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T18" s="2" t="s">
@@ -5577,7 +5577,7 @@
       <c r="C19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -5586,7 +5586,7 @@
       <c r="F19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -5595,7 +5595,7 @@
       <c r="I19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K19" s="2" t="s">
@@ -5604,7 +5604,7 @@
       <c r="L19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="M19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N19" s="2" t="s">
@@ -5613,7 +5613,7 @@
       <c r="O19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P19" s="3" t="s">
+      <c r="P19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q19" s="2" t="s">
@@ -5622,7 +5622,7 @@
       <c r="R19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="S19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T19" s="2" t="s">
@@ -5642,7 +5642,7 @@
       <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -5651,7 +5651,7 @@
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -5660,7 +5660,7 @@
       <c r="I20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -5669,7 +5669,7 @@
       <c r="L20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="M20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N20" s="2" t="s">
@@ -5678,7 +5678,7 @@
       <c r="O20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P20" s="3" t="s">
+      <c r="P20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q20" s="2" t="s">
@@ -5687,7 +5687,7 @@
       <c r="R20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="S20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T20" s="2" t="s">
@@ -5707,7 +5707,7 @@
       <c r="C21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -5716,7 +5716,7 @@
       <c r="F21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -5725,7 +5725,7 @@
       <c r="I21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K21" s="2" t="s">
@@ -5734,7 +5734,7 @@
       <c r="L21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="M21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N21" s="2" t="s">
@@ -5743,7 +5743,7 @@
       <c r="O21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="P21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q21" s="2" t="s">
@@ -5752,7 +5752,7 @@
       <c r="R21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="S21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T21" s="2" t="s">
@@ -5775,55 +5775,55 @@
       <c r="D22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="H22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="3" t="s">
+      <c r="K22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O22" s="3" t="s">
+      <c r="N22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R22" s="3" t="s">
+      <c r="Q22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="S22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U22" s="3" t="s">
+      <c r="T22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U22" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -2917,7 +2917,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -2939,7 +2939,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -2961,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -2983,7 +2983,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
@@ -2994,7 +2994,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
@@ -3005,7 +3005,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>22</v>
@@ -3016,7 +3016,7 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
@@ -3027,7 +3027,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -3038,7 +3038,7 @@
         <v>29</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -3049,7 +3049,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -3060,7 +3060,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -11,14 +11,16 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Score view" r:id="rId8" sheetId="6"/>
+    <sheet name="Infeasible view" r:id="rId8" sheetId="6"/>
     <sheet name="Rooms view" r:id="rId9" sheetId="7"/>
     <sheet name="Speakers view" r:id="rId10" sheetId="8"/>
     <sheet name="Theme tracks view" r:id="rId11" sheetId="9"/>
     <sheet name="Sectors view" r:id="rId12" sheetId="10"/>
-    <sheet name="Audience type view" r:id="rId13" sheetId="11"/>
-    <sheet name="Audience level view" r:id="rId14" sheetId="12"/>
+    <sheet name="Audience types view" r:id="rId13" sheetId="11"/>
+    <sheet name="Audience levels view" r:id="rId14" sheetId="12"/>
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
+    <sheet name="Languages view" r:id="rId16" sheetId="14"/>
+    <sheet name="Score view" r:id="rId17" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -31,9 +33,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S146: Tuning IOT-driven Weld
-  Hugo V. Jones
-  PINNED BY USER</t>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -48,9 +51,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S146: Tuning IOT-driven Weld
-  Hugo V. Jones
-  PINNED BY USER</t>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -65,9 +69,28 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S146: Tuning IOT-driven Weld
-  Hugo V. Jones
-  PINNED BY USER</t>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -82,9 +105,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S146: Tuning IOT-driven Weld
-  Hugo V. Jones
-  PINNED BY USER</t>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -99,9 +123,10 @@
   <commentList>
     <comment ref="C70" authorId="0">
       <text>
-        <t>S146: Tuning IOT-driven Weld
-  Hugo V. Jones
-  PINNED BY USER</t>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -116,16 +141,18 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S146: Tuning IOT-driven Weld
-  Hugo V. Jones
-  PINNED BY USER</t>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0">
       <text>
-        <t>S146: Tuning IOT-driven Weld
-  Hugo V. Jones
-  PINNED BY USER</t>
+        <t xml:space="preserve">S146: Tuning IOT-driven Weld
+    Hugo V. Jones
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -133,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12621" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12683" uniqueCount="864">
   <si>
     <t>Conference name</t>
   </si>
@@ -2717,6 +2744,15 @@
   </si>
   <si>
     <t>S146 (level 1)</t>
+  </si>
+  <si>
+    <t>Constraint match</t>
+  </si>
+  <si>
+    <t>Match score</t>
+  </si>
+  <si>
+    <t>Total score</t>
   </si>
 </sst>
 </file>
@@ -2828,6 +2864,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
@@ -4025,6 +4069,261 @@
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="true">
+      <c r="A3" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="16.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="12.296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.08203125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>863</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -33534,7 +33833,7 @@
         <v>20.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>360.0</v>
+        <v>216.0</v>
       </c>
     </row>
   </sheetData>
@@ -33709,7 +34008,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" ht="60.0" customHeight="true">
+    <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
         <v>84</v>
       </c>
@@ -33768,7 +34067,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" ht="60.0" customHeight="true">
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
         <v>86</v>
       </c>
@@ -33827,7 +34126,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" ht="60.0" customHeight="true">
+    <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
         <v>87</v>
       </c>
@@ -33886,7 +34185,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" ht="60.0" customHeight="true">
+    <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
         <v>89</v>
       </c>
@@ -33945,7 +34244,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" ht="60.0" customHeight="true">
+    <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
         <v>90</v>
       </c>
@@ -34004,7 +34303,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" ht="60.0" customHeight="true">
+    <row r="8" ht="45.0" customHeight="true">
       <c r="A8" s="2" t="s">
         <v>91</v>
       </c>
@@ -34063,7 +34362,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" ht="60.0" customHeight="true">
+    <row r="9" ht="45.0" customHeight="true">
       <c r="A9" s="2" t="s">
         <v>92</v>
       </c>
@@ -34122,7 +34421,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" ht="60.0" customHeight="true">
+    <row r="10" ht="45.0" customHeight="true">
       <c r="A10" s="2" t="s">
         <v>93</v>
       </c>
@@ -34181,7 +34480,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" ht="60.0" customHeight="true">
+    <row r="11" ht="45.0" customHeight="true">
       <c r="A11" s="2" t="s">
         <v>94</v>
       </c>
@@ -34240,7 +34539,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" ht="60.0" customHeight="true">
+    <row r="12" ht="45.0" customHeight="true">
       <c r="A12" s="2" t="s">
         <v>95</v>
       </c>
@@ -34299,7 +34598,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" ht="60.0" customHeight="true">
+    <row r="13" ht="45.0" customHeight="true">
       <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
@@ -34358,7 +34657,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" ht="60.0" customHeight="true">
+    <row r="14" ht="45.0" customHeight="true">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -34417,7 +34716,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" ht="60.0" customHeight="true">
+    <row r="15" ht="45.0" customHeight="true">
       <c r="A15" s="2" t="s">
         <v>98</v>
       </c>
@@ -34476,7 +34775,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" ht="60.0" customHeight="true">
+    <row r="16" ht="45.0" customHeight="true">
       <c r="A16" s="2" t="s">
         <v>99</v>
       </c>
@@ -34535,7 +34834,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" ht="60.0" customHeight="true">
+    <row r="17" ht="45.0" customHeight="true">
       <c r="A17" s="2" t="s">
         <v>100</v>
       </c>
@@ -34594,7 +34893,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" ht="60.0" customHeight="true">
+    <row r="18" ht="45.0" customHeight="true">
       <c r="A18" s="2" t="s">
         <v>101</v>
       </c>
@@ -34653,7 +34952,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" ht="60.0" customHeight="true">
+    <row r="19" ht="45.0" customHeight="true">
       <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
@@ -34712,7 +35011,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" ht="60.0" customHeight="true">
+    <row r="20" ht="45.0" customHeight="true">
       <c r="A20" s="2" t="s">
         <v>103</v>
       </c>
@@ -34771,7 +35070,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" ht="60.0" customHeight="true">
+    <row r="21" ht="45.0" customHeight="true">
       <c r="A21" s="2" t="s">
         <v>104</v>
       </c>
@@ -34830,7 +35129,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" ht="60.0" customHeight="true">
+    <row r="22" ht="45.0" customHeight="true">
       <c r="A22" s="2" t="s">
         <v>105</v>
       </c>
@@ -34910,24 +35209,43 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="20.0" customWidth="true"/>
+    <col min="3" max="3" width="20.0" customWidth="true"/>
+    <col min="4" max="4" width="20.0" customWidth="true"/>
+    <col min="5" max="5" width="20.0" customWidth="true"/>
+    <col min="6" max="6" width="20.0" customWidth="true"/>
+    <col min="7" max="7" width="20.0" customWidth="true"/>
+    <col min="8" max="8" width="20.0" customWidth="true"/>
+    <col min="9" max="9" width="20.0" customWidth="true"/>
+    <col min="10" max="10" width="20.0" customWidth="true"/>
+    <col min="11" max="11" width="20.0" customWidth="true"/>
+    <col min="12" max="12" width="20.0" customWidth="true"/>
+    <col min="13" max="13" width="20.0" customWidth="true"/>
+    <col min="14" max="14" width="20.0" customWidth="true"/>
+    <col min="15" max="15" width="20.0" customWidth="true"/>
+    <col min="16" max="16" width="20.0" customWidth="true"/>
+    <col min="17" max="17" width="20.0" customWidth="true"/>
+    <col min="18" max="18" width="20.0" customWidth="true"/>
+    <col min="19" max="19" width="20.0" customWidth="true"/>
+    <col min="20" max="20" width="20.0" customWidth="true"/>
+    <col min="21" max="21" width="20.0" customWidth="true"/>
+    <col min="22" max="22" width="20.0" customWidth="true"/>
+    <col min="23" max="23" width="20.0" customWidth="true"/>
+    <col min="24" max="24" width="20.0" customWidth="true"/>
+    <col min="25" max="25" width="20.0" customWidth="true"/>
+    <col min="26" max="26" width="20.0" customWidth="true"/>
+    <col min="27" max="27" width="20.0" customWidth="true"/>
+    <col min="28" max="28" width="20.0" customWidth="true"/>
+    <col min="29" max="29" width="20.0" customWidth="true"/>
+    <col min="30" max="30" width="20.0" customWidth="true"/>
+    <col min="31" max="31" width="20.0" customWidth="true"/>
+    <col min="32" max="32" width="20.0" customWidth="true"/>
+    <col min="33" max="33" width="20.0" customWidth="true"/>
+    <col min="34" max="34" width="20.0" customWidth="true"/>
+    <col min="35" max="35" width="20.0" customWidth="true"/>
+    <col min="36" max="36" width="20.0" customWidth="true"/>
+    <col min="37" max="37" width="20.0" customWidth="true"/>
+    <col min="38" max="38" width="20.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -217,40 +217,40 @@
     <t>Soft reward per 2 talks that have the same timeslot and a different language</t>
   </si>
   <si>
-    <t>Speaker preferred timeslot tag</t>
+    <t>Speaker preferred timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker undesired timeslot tag</t>
+    <t>Speaker undesired timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk preferred timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk undesired timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker preferred room tag</t>
+    <t>Talk preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker preferred room tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker undesired room tag</t>
+    <t>Speaker undesired room tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk preferred room tag</t>
-  </si>
-  <si>
-    <t>Talk undesired room tag</t>
+    <t>Talk preferred room tags</t>
+  </si>
+  <si>
+    <t>Talk undesired room tags</t>
   </si>
   <si>
     <t>Same day talks</t>
@@ -301,43 +301,43 @@
     <t>Hard penalty per pair of talks with the same speaker in overlapping timeslots</t>
   </si>
   <si>
-    <t>Speaker required timeslot tag</t>
+    <t>Speaker required timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker prohibited timeslot tag</t>
+    <t>Speaker prohibited timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk required timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker required room tag</t>
+    <t>Talk required timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker required room tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker prohibited room tag</t>
+    <t>Speaker prohibited room tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk required room tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited room tag</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tag</t>
+    <t>Talk required room tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited room tags</t>
+  </si>
+  <si>
+    <t>Talk mutually-exclusive-talks tags</t>
   </si>
   <si>
     <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -276,7 +276,7 @@
     <t>Popular talks</t>
   </si>
   <si>
-    <t>Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
+    <t>Soft penalty per 2 talks where the less popular one (has lower favorite count) is assigned a larger room than the more popular talk</t>
   </si>
   <si>
     <t>Crowd control</t>
@@ -1017,7 +1017,7 @@
     <t>Prerequisite talks codes</t>
   </si>
   <si>
-    <t>Number of likes</t>
+    <t>Favorite count</t>
   </si>
   <si>
     <t>Crowd control risk</t>
@@ -18533,7 +18533,7 @@
     <col min="18" max="18" width="22.84375" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="31.2734375" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="26.23046875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.5390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="16.25390625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="20.140625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.65234375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.14453125" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -21,6 +21,9 @@
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
     <sheet name="Languages view" r:id="rId16" sheetId="14"/>
     <sheet name="Score view" r:id="rId17" sheetId="15"/>
+    <sheet name="Mon 2018-10-01" r:id="rId18" sheetId="16"/>
+    <sheet name="Tue 2018-10-02" r:id="rId19" sheetId="17"/>
+    <sheet name="Wed 2018-10-03" r:id="rId20" sheetId="18"/>
   </sheets>
 </workbook>
 </file>
@@ -33,11 +36,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S056: Deliver stable JUnit
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
     Hugo V. King
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -53,11 +55,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S056: Deliver stable JUnit
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
     Hugo V. King
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -73,11 +74,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S056: Deliver stable JUnit
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
     Hugo V. King
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -93,7 +93,26 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S056: Deliver stable JUnit
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
+    Hugo V. King
+PINNED BY USER
+-10soft total
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
     Hugo V. King
 PINNED BY USER
 -10soft total
@@ -113,7 +132,7 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S056: Deliver stable JUnit
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
     Hugo V. King
 PINNED BY USER
 -10soft total
@@ -133,11 +152,10 @@
   <commentList>
     <comment ref="C80" authorId="0">
       <text>
-        <t xml:space="preserve">S056: Deliver stable JUnit
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
     Hugo V. King
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -153,11 +171,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S056: Deliver stable JUnit
+        <t xml:space="preserve">S056-IoT: Deliver stable JUnit
     Hugo V. King
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -166,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13105" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13133" uniqueCount="879">
   <si>
     <t>Conference name</t>
   </si>
@@ -285,6 +302,12 @@
     <t>Soft penalty per talks with crowd control risk greater than zero that are not in pairs</t>
   </si>
   <si>
+    <t>Talk mutually-exclusive-talks tags</t>
+  </si>
+  <si>
+    <t>Medium penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
+  </si>
+  <si>
     <t>Talk type of timeslot</t>
   </si>
   <si>
@@ -355,12 +378,6 @@
   </si>
   <si>
     <t>Talk prohibited room tags</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tags</t>
-  </si>
-  <si>
-    <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
   </si>
   <si>
     <t>Talk prerequisite talks</t>
@@ -2801,6 +2818,10 @@
   </si>
   <si>
     <t xml:space="preserve">    S056</t>
+  </si>
+  <si>
+    <t>Deliver stable JUnit
+Hugo V. King</t>
   </si>
 </sst>
 </file>
@@ -2822,7 +2843,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2857,6 +2878,46 @@
         <fgColor rgb="FCAF3E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="8AE234"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCE94F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="729FCF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="E9B96E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="73D216"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="EDD400"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="3465A4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="C17D11"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2870,7 +2931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment wrapText="true" vertical="center"/>
@@ -2894,6 +2955,33 @@
       <alignment wrapText="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2925,6 +3013,18 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
@@ -2962,7 +3062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.66796875" customWidth="true" bestFit="true"/>
@@ -3205,109 +3305,99 @@
         <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10000.0</v>
+        <v>1.0</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>10000.0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>10.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -3318,40 +3408,40 @@
         <v>1.0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -3362,17 +3452,28 @@
         <v>1.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3387,7 +3488,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
@@ -3545,7 +3646,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
@@ -3763,7 +3864,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.3046875" customWidth="true" bestFit="true"/>
@@ -3981,7 +4082,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="13.4609375" customWidth="true" bestFit="true"/>
@@ -4199,7 +4300,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.3046875" customWidth="true" bestFit="true"/>
@@ -4399,12 +4500,6 @@
       <c r="S3" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>858</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -4423,44 +4518,231 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.0703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.15625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>875</v>
-      </c>
-    </row>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="4">
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.3515625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.12890625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -4470,7 +4752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.3828125" customWidth="true" bestFit="true"/>
@@ -4811,7 +5093,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
@@ -6347,7 +6629,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AB146"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.76953125" customWidth="true" bestFit="true"/>
@@ -18510,7 +18792,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AB217"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
@@ -36564,7 +36846,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.78515625" customWidth="true" bestFit="true"/>
@@ -36663,7 +36945,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.02734375" customWidth="true" bestFit="true"/>
@@ -38021,7 +38303,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T146"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.76953125" customWidth="true" bestFit="true"/>
@@ -46695,7 +46977,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/216talks-18timeslots-20rooms.xlsx
@@ -47,7 +47,7 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
 </t>
       </text>
     </comment>
@@ -66,7 +66,7 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
 </t>
       </text>
     </comment>
@@ -93,7 +93,7 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
 </t>
       </text>
     </comment>
@@ -128,7 +128,7 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
 </t>
       </text>
     </comment>
@@ -147,10 +147,9 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
     -1650soft for 1 Popular talkss
         S013
-    -900soft for 1 Talk preferred room tagss
 </t>
       </text>
     </comment>
@@ -179,10 +178,9 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
     -1650soft for 1 Popular talkss
         S013
-    -900soft for 1 Talk preferred room tagss
 </t>
       </text>
     </comment>
@@ -219,7 +217,7 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
 </t>
       </text>
     </comment>
@@ -228,7 +226,7 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
 </t>
       </text>
     </comment>
@@ -247,7 +245,7 @@
         <t xml:space="preserve">S186-Mobile: Tuning IOT-driven Android
     Chad R. Li, Dan S. Poe
 PINNED BY USER
--2550soft total
+-1650soft total
 </t>
       </text>
     </comment>
@@ -264,7 +262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14329" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14327" uniqueCount="926">
   <si>
     <t>Conference name</t>
   </si>
@@ -1268,9 +1266,6 @@
     <t>OptaPlanner</t>
   </si>
   <si>
-    <t>Large, Recorded</t>
-  </si>
-  <si>
     <t>S005</t>
   </si>
   <si>
@@ -2927,7 +2922,7 @@
     <t>Score</t>
   </si>
   <si>
-    <t>-428init/-2550soft</t>
+    <t>-428init/-1650soft</t>
   </si>
   <si>
     <t>Count</t>
@@ -3029,9 +3024,6 @@
   </si>
   <si>
     <t>20soft</t>
-  </si>
-  <si>
-    <t>-900soft</t>
   </si>
   <si>
     <t>10soft</t>
@@ -3855,7 +3847,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -4013,7 +4005,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -4075,10 +4067,10 @@
         <v>321</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>896</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>897</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -4290,13 +4282,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -4349,10 +4341,10 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>93</v>
@@ -4508,7 +4500,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -4567,13 +4559,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -4626,10 +4618,10 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>93</v>
@@ -4847,10 +4839,10 @@
         <v>316</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>896</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>897</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -4918,7 +4910,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.6484375" customWidth="true" bestFit="true"/>
@@ -4932,39 +4924,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>886</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4977,13 +4969,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6">
@@ -4991,13 +4983,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -5005,13 +4997,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="8">
@@ -5019,13 +5011,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="9">
@@ -5033,13 +5025,13 @@
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="10">
@@ -5047,13 +5039,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="11">
@@ -5061,13 +5053,13 @@
         <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="12">
@@ -5075,13 +5067,13 @@
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="13">
@@ -5089,13 +5081,13 @@
         <v>35</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="14">
@@ -5103,13 +5095,13 @@
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="15">
@@ -5117,13 +5109,13 @@
         <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="16">
@@ -5131,13 +5123,13 @@
         <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="17">
@@ -5145,13 +5137,13 @@
         <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="18">
@@ -5159,13 +5151,13 @@
         <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="19">
@@ -5173,13 +5165,13 @@
         <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="20">
@@ -5187,13 +5179,13 @@
         <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="21">
@@ -5201,13 +5193,13 @@
         <v>62</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="22">
@@ -5215,13 +5207,13 @@
         <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="23">
@@ -5229,13 +5221,13 @@
         <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="24">
@@ -5243,13 +5235,13 @@
         <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="25">
@@ -5257,13 +5249,13 @@
         <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="26">
@@ -5271,13 +5263,13 @@
         <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
     </row>
     <row r="27">
@@ -5285,13 +5277,13 @@
         <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="28">
@@ -5299,13 +5291,13 @@
         <v>83</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="29">
@@ -5313,13 +5305,13 @@
         <v>77</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="30">
@@ -5327,13 +5319,13 @@
         <v>60</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="31">
@@ -5341,13 +5333,13 @@
         <v>65</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="32">
@@ -5355,13 +5347,13 @@
         <v>69</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="33">
@@ -5369,13 +5361,13 @@
         <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="34">
@@ -5383,13 +5375,13 @@
         <v>67</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="35">
@@ -5397,13 +5389,13 @@
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="36">
@@ -5411,13 +5403,13 @@
         <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="37">
@@ -5425,13 +5417,13 @@
         <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="38">
@@ -5439,13 +5431,13 @@
         <v>58</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="39">
@@ -5453,13 +5445,13 @@
         <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="40">
@@ -5467,13 +5459,13 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="41">
@@ -5481,13 +5473,13 @@
         <v>26</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="42"/>
@@ -5497,13 +5489,13 @@
         <v>69</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="45">
@@ -5513,406 +5505,407 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>817</v>
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>922</v>
+        <v>912</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>916</v>
@@ -5921,82 +5914,82 @@
         <v>0.0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>920</v>
@@ -6005,35 +5998,21 @@
         <v>0.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -6074,7 +6053,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
@@ -6082,7 +6061,7 @@
         <v>109</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -20462,7 +20441,7 @@
         <v>93</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>93</v>
@@ -20649,16 +20628,16 @@
         <v>93</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>93</v>
@@ -20842,7 +20821,7 @@
         <v>93</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>93</v>
@@ -20892,19 +20871,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -20916,7 +20895,7 @@
         <v>3.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>316</v>
@@ -20987,10 +20966,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>92</v>
@@ -21002,7 +20981,7 @@
         <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>321</v>
@@ -21011,7 +20990,7 @@
         <v>2.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>316</v>
@@ -21029,7 +21008,7 @@
         <v>93</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>93</v>
@@ -21038,7 +21017,7 @@
         <v>93</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>93</v>
@@ -21082,19 +21061,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -21106,7 +21085,7 @@
         <v>3.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>316</v>
@@ -21177,10 +21156,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>92</v>
@@ -21189,7 +21168,7 @@
         <v>156</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -21201,7 +21180,7 @@
         <v>2.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>316</v>
@@ -21222,7 +21201,7 @@
         <v>93</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>93</v>
@@ -21272,19 +21251,19 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>313</v>
@@ -21296,7 +21275,7 @@
         <v>1.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>316</v>
@@ -21317,7 +21296,7 @@
         <v>93</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>93</v>
@@ -21367,22 +21346,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>329</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>321</v>
@@ -21391,7 +21370,7 @@
         <v>2.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>316</v>
@@ -21412,7 +21391,7 @@
         <v>93</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>93</v>
@@ -21462,10 +21441,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>92</v>
@@ -21474,7 +21453,7 @@
         <v>161</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -21486,7 +21465,7 @@
         <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>316</v>
@@ -21507,7 +21486,7 @@
         <v>93</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>93</v>
@@ -21557,16 +21536,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>320</v>
@@ -21581,7 +21560,7 @@
         <v>3.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>316</v>
@@ -21602,7 +21581,7 @@
         <v>93</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>93</v>
@@ -21652,10 +21631,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>92</v>
@@ -21664,7 +21643,7 @@
         <v>164</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -21676,7 +21655,7 @@
         <v>2.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>316</v>
@@ -21697,7 +21676,7 @@
         <v>93</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>93</v>
@@ -21747,10 +21726,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>92</v>
@@ -21759,7 +21738,7 @@
         <v>165</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -21771,7 +21750,7 @@
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>316</v>
@@ -21804,7 +21783,7 @@
         <v>93</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U16" s="2" t="n">
         <v>309.0</v>
@@ -21842,10 +21821,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>92</v>
@@ -21854,7 +21833,7 @@
         <v>166</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -21866,7 +21845,7 @@
         <v>3.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>316</v>
@@ -21887,13 +21866,13 @@
         <v>93</v>
       </c>
       <c r="P17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>93</v>
@@ -21937,16 +21916,16 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>320</v>
@@ -21961,7 +21940,7 @@
         <v>1.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>316</v>
@@ -21982,7 +21961,7 @@
         <v>93</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>93</v>
@@ -22032,10 +22011,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>92</v>
@@ -22044,7 +22023,7 @@
         <v>169</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -22056,7 +22035,7 @@
         <v>3.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>316</v>
@@ -22127,19 +22106,19 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -22151,7 +22130,7 @@
         <v>2.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>316</v>
@@ -22222,16 +22201,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>320</v>
@@ -22246,7 +22225,7 @@
         <v>3.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>316</v>
@@ -22267,7 +22246,7 @@
         <v>93</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>93</v>
@@ -22317,19 +22296,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -22362,7 +22341,7 @@
         <v>93</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>93</v>
@@ -22412,10 +22391,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>92</v>
@@ -22507,19 +22486,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -22602,10 +22581,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>92</v>
@@ -22647,7 +22626,7 @@
         <v>93</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>93</v>
@@ -22697,10 +22676,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>95</v>
@@ -22709,7 +22688,7 @@
         <v>180</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -22721,7 +22700,7 @@
         <v>2.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>316</v>
@@ -22792,10 +22771,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>95</v>
@@ -22816,7 +22795,7 @@
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>316</v>
@@ -22837,7 +22816,7 @@
         <v>93</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>93</v>
@@ -22887,10 +22866,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>95</v>
@@ -22899,7 +22878,7 @@
         <v>182</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -22911,7 +22890,7 @@
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>316</v>
@@ -22982,19 +22961,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -23006,7 +22985,7 @@
         <v>1.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>316</v>
@@ -23027,7 +23006,7 @@
         <v>93</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>93</v>
@@ -23077,19 +23056,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -23101,7 +23080,7 @@
         <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>316</v>
@@ -23172,19 +23151,19 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -23196,7 +23175,7 @@
         <v>1.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>316</v>
@@ -23217,7 +23196,7 @@
         <v>93</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q31" s="2" t="s">
         <v>93</v>
@@ -23267,10 +23246,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>95</v>
@@ -23279,7 +23258,7 @@
         <v>189</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>93</v>
@@ -23291,7 +23270,7 @@
         <v>3.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>316</v>
@@ -23312,7 +23291,7 @@
         <v>93</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>93</v>
@@ -23362,16 +23341,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>312</v>
@@ -23386,7 +23365,7 @@
         <v>3.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>316</v>
@@ -23457,10 +23436,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>95</v>
@@ -23469,10 +23448,10 @@
         <v>192</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>314</v>
@@ -23481,7 +23460,7 @@
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>316</v>
@@ -23552,10 +23531,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>95</v>
@@ -23564,7 +23543,7 @@
         <v>193</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>93</v>
@@ -23576,7 +23555,7 @@
         <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>316</v>
@@ -23597,7 +23576,7 @@
         <v>93</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q35" s="2" t="s">
         <v>93</v>
@@ -23647,19 +23626,19 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>93</v>
@@ -23671,7 +23650,7 @@
         <v>3.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>316</v>
@@ -23742,10 +23721,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>95</v>
@@ -23754,7 +23733,7 @@
         <v>196</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>93</v>
@@ -23766,7 +23745,7 @@
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>316</v>
@@ -23837,10 +23816,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>95</v>
@@ -23849,10 +23828,10 @@
         <v>197</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>325</v>
@@ -23861,7 +23840,7 @@
         <v>2.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>316</v>
@@ -23882,13 +23861,13 @@
         <v>93</v>
       </c>
       <c r="P38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R38" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>93</v>
@@ -23932,10 +23911,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>95</v>
@@ -23944,7 +23923,7 @@
         <v>198</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>93</v>
@@ -23956,7 +23935,7 @@
         <v>3.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>316</v>
@@ -24027,10 +24006,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>95</v>
@@ -24039,7 +24018,7 @@
         <v>199</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>93</v>
@@ -24051,7 +24030,7 @@
         <v>3.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>316</v>
@@ -24122,19 +24101,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>93</v>
@@ -24146,7 +24125,7 @@
         <v>1.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>316</v>
@@ -24167,13 +24146,13 @@
         <v>93</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>93</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="S41" s="2" t="s">
         <v>93</v>
@@ -24217,10 +24196,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>95</v>
@@ -24229,7 +24208,7 @@
         <v>202</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>93</v>
@@ -24262,7 +24241,7 @@
         <v>93</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>93</v>
@@ -24312,16 +24291,16 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>312</v>
@@ -24407,16 +24386,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>329</v>
@@ -24449,7 +24428,7 @@
         <v>93</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>93</v>
@@ -24458,7 +24437,7 @@
         <v>93</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>93</v>
@@ -24502,10 +24481,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>95</v>
@@ -24526,7 +24505,7 @@
         <v>2.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>316</v>
@@ -24597,19 +24576,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>93</v>
@@ -24621,7 +24600,7 @@
         <v>3.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>316</v>
@@ -24642,7 +24621,7 @@
         <v>93</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>93</v>
@@ -24692,10 +24671,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>95</v>
@@ -24704,7 +24683,7 @@
         <v>210</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>93</v>
@@ -24716,7 +24695,7 @@
         <v>3.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>316</v>
@@ -24787,10 +24766,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>95</v>
@@ -24799,10 +24778,10 @@
         <v>211</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>314</v>
@@ -24811,7 +24790,7 @@
         <v>3.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>316</v>
@@ -24832,7 +24811,7 @@
         <v>93</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q48" s="2" t="s">
         <v>93</v>
@@ -24882,19 +24861,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>93</v>
@@ -24906,7 +24885,7 @@
         <v>3.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>316</v>
@@ -24977,16 +24956,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>320</v>
@@ -25001,7 +24980,7 @@
         <v>2.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>316</v>
@@ -25022,7 +25001,7 @@
         <v>93</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q50" s="2" t="s">
         <v>93</v>
@@ -25072,19 +25051,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>93</v>
@@ -25096,7 +25075,7 @@
         <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>316</v>
@@ -25167,10 +25146,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>95</v>
@@ -25179,7 +25158,7 @@
         <v>219</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>93</v>
@@ -25191,7 +25170,7 @@
         <v>1.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>316</v>
@@ -25212,7 +25191,7 @@
         <v>93</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>93</v>
@@ -25262,10 +25241,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>95</v>
@@ -25286,7 +25265,7 @@
         <v>3.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>316</v>
@@ -25307,7 +25286,7 @@
         <v>93</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>93</v>
@@ -25357,10 +25336,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>95</v>
@@ -25369,7 +25348,7 @@
         <v>221</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>93</v>
@@ -25381,7 +25360,7 @@
         <v>1.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>316</v>
@@ -25452,10 +25431,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>95</v>
@@ -25464,7 +25443,7 @@
         <v>222</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>93</v>
@@ -25476,7 +25455,7 @@
         <v>1.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>316</v>
@@ -25500,10 +25479,10 @@
         <v>93</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="S55" s="2" t="s">
         <v>93</v>
@@ -25547,19 +25526,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>93</v>
@@ -25571,7 +25550,7 @@
         <v>2.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>316</v>
@@ -25592,7 +25571,7 @@
         <v>93</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>93</v>
@@ -25642,19 +25621,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>93</v>
@@ -25666,7 +25645,7 @@
         <v>3.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>316</v>
@@ -25687,7 +25666,7 @@
         <v>93</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>93</v>
@@ -25737,10 +25716,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>95</v>
@@ -25749,10 +25728,10 @@
         <v>228</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>314</v>
@@ -25761,7 +25740,7 @@
         <v>3.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>316</v>
@@ -25782,7 +25761,7 @@
         <v>93</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q58" s="2" t="s">
         <v>93</v>
@@ -25832,22 +25811,22 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>321</v>
@@ -25856,7 +25835,7 @@
         <v>2.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>316</v>
@@ -25877,7 +25856,7 @@
         <v>93</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q59" s="2" t="s">
         <v>93</v>
@@ -25927,16 +25906,16 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>312</v>
@@ -25951,7 +25930,7 @@
         <v>2.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>316</v>
@@ -25972,7 +25951,7 @@
         <v>93</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q60" s="2" t="s">
         <v>93</v>
@@ -26022,10 +26001,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>95</v>
@@ -26034,7 +26013,7 @@
         <v>233</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>93</v>
@@ -26064,7 +26043,7 @@
         <v>93</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>93</v>
@@ -26073,7 +26052,7 @@
         <v>93</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S61" s="2" t="s">
         <v>93</v>
@@ -26117,10 +26096,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>95</v>
@@ -26129,10 +26108,10 @@
         <v>234</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>321</v>
@@ -26212,19 +26191,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>313</v>
@@ -26257,7 +26236,7 @@
         <v>93</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>93</v>
@@ -26307,10 +26286,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>95</v>
@@ -26319,7 +26298,7 @@
         <v>237</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>93</v>
@@ -26331,7 +26310,7 @@
         <v>3.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>316</v>
@@ -26352,7 +26331,7 @@
         <v>93</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q64" s="2" t="s">
         <v>93</v>
@@ -26402,19 +26381,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>93</v>
@@ -26426,7 +26405,7 @@
         <v>1.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>316</v>
@@ -26497,10 +26476,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>95</v>
@@ -26509,7 +26488,7 @@
         <v>240</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>93</v>
@@ -26521,7 +26500,7 @@
         <v>3.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>316</v>
@@ -26592,22 +26571,22 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>524</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>321</v>
@@ -26616,7 +26595,7 @@
         <v>3.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>316</v>
@@ -26637,7 +26616,7 @@
         <v>93</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q67" s="2" t="s">
         <v>93</v>
@@ -26687,10 +26666,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>95</v>
@@ -26699,10 +26678,10 @@
         <v>244</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>321</v>
@@ -26711,7 +26690,7 @@
         <v>1.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>316</v>
@@ -26782,10 +26761,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>95</v>
@@ -26794,7 +26773,7 @@
         <v>245</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>93</v>
@@ -26806,7 +26785,7 @@
         <v>2.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>316</v>
@@ -26877,10 +26856,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>95</v>
@@ -26889,7 +26868,7 @@
         <v>246</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>93</v>
@@ -26901,7 +26880,7 @@
         <v>3.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>316</v>
@@ -26922,7 +26901,7 @@
         <v>93</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q70" s="2" t="s">
         <v>93</v>
@@ -26972,19 +26951,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>533</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>93</v>
@@ -26996,7 +26975,7 @@
         <v>3.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>316</v>
@@ -27026,7 +27005,7 @@
         <v>93</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>93</v>
@@ -27067,10 +27046,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>95</v>
@@ -27079,10 +27058,10 @@
         <v>249</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>314</v>
@@ -27091,7 +27070,7 @@
         <v>3.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>316</v>
@@ -27121,7 +27100,7 @@
         <v>93</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T72" s="2" t="s">
         <v>93</v>
@@ -27162,10 +27141,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>95</v>
@@ -27174,7 +27153,7 @@
         <v>250</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>93</v>
@@ -27186,7 +27165,7 @@
         <v>1.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>316</v>
@@ -27257,19 +27236,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>93</v>
@@ -27281,7 +27260,7 @@
         <v>1.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>316</v>
@@ -27302,7 +27281,7 @@
         <v>93</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q74" s="2" t="s">
         <v>93</v>
@@ -27352,10 +27331,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>95</v>
@@ -27364,7 +27343,7 @@
         <v>253</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>93</v>
@@ -27376,7 +27355,7 @@
         <v>1.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>316</v>
@@ -27397,7 +27376,7 @@
         <v>93</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q75" s="2" t="s">
         <v>93</v>
@@ -27447,10 +27426,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>95</v>
@@ -27459,7 +27438,7 @@
         <v>254</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>93</v>
@@ -27471,7 +27450,7 @@
         <v>2.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>316</v>
@@ -27492,7 +27471,7 @@
         <v>93</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q76" s="2" t="s">
         <v>93</v>
@@ -27542,10 +27521,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>95</v>
@@ -27554,7 +27533,7 @@
         <v>255</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>313</v>
@@ -27566,7 +27545,7 @@
         <v>2.0</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>316</v>
@@ -27637,19 +27616,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>93</v>
@@ -27661,7 +27640,7 @@
         <v>2.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>316</v>
@@ -27732,10 +27711,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>95</v>
@@ -27777,7 +27756,7 @@
         <v>93</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q79" s="2" t="s">
         <v>93</v>
@@ -27827,19 +27806,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>93</v>
@@ -27872,7 +27851,7 @@
         <v>93</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>93</v>
@@ -27922,10 +27901,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>95</v>
@@ -28017,10 +27996,10 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>95</v>
@@ -28029,7 +28008,7 @@
         <v>262</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>93</v>
@@ -28112,10 +28091,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>95</v>
@@ -28124,7 +28103,7 @@
         <v>263</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>93</v>
@@ -28136,7 +28115,7 @@
         <v>3.0</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>316</v>
@@ -28207,10 +28186,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>95</v>
@@ -28219,7 +28198,7 @@
         <v>264</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>93</v>
@@ -28231,7 +28210,7 @@
         <v>2.0</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>316</v>
@@ -28252,7 +28231,7 @@
         <v>93</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q84" s="2" t="s">
         <v>93</v>
@@ -28302,10 +28281,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>95</v>
@@ -28326,7 +28305,7 @@
         <v>1.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>316</v>
@@ -28347,7 +28326,7 @@
         <v>93</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q85" s="2" t="s">
         <v>93</v>
@@ -28397,10 +28376,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>95</v>
@@ -28409,7 +28388,7 @@
         <v>266</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>93</v>
@@ -28421,7 +28400,7 @@
         <v>1.0</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>316</v>
@@ -28442,7 +28421,7 @@
         <v>93</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q86" s="2" t="s">
         <v>93</v>
@@ -28492,19 +28471,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>93</v>
@@ -28516,7 +28495,7 @@
         <v>1.0</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>316</v>
@@ -28587,10 +28566,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>95</v>
@@ -28611,7 +28590,7 @@
         <v>2.0</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>316</v>
@@ -28632,7 +28611,7 @@
         <v>93</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q88" s="2" t="s">
         <v>93</v>
@@ -28682,19 +28661,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>93</v>
@@ -28706,7 +28685,7 @@
         <v>3.0</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>316</v>
@@ -28727,13 +28706,13 @@
         <v>93</v>
       </c>
       <c r="P89" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q89" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R89" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="Q89" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R89" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S89" s="2" t="s">
         <v>93</v>
@@ -28777,10 +28756,10 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>95</v>
@@ -28789,10 +28768,10 @@
         <v>272</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>321</v>
@@ -28801,7 +28780,7 @@
         <v>3.0</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>316</v>
@@ -28822,7 +28801,7 @@
         <v>93</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q90" s="2" t="s">
         <v>93</v>
@@ -28872,10 +28851,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>95</v>
@@ -28884,7 +28863,7 @@
         <v>273</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>93</v>
@@ -28896,7 +28875,7 @@
         <v>2.0</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>316</v>
@@ -28917,7 +28896,7 @@
         <v>93</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q91" s="2" t="s">
         <v>93</v>
@@ -28967,10 +28946,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>95</v>
@@ -28982,7 +28961,7 @@
         <v>329</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>314</v>
@@ -28991,7 +28970,7 @@
         <v>1.0</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>316</v>
@@ -29012,7 +28991,7 @@
         <v>93</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q92" s="2" t="s">
         <v>93</v>
@@ -29062,19 +29041,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>93</v>
@@ -29086,7 +29065,7 @@
         <v>2.0</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>316</v>
@@ -29157,10 +29136,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>95</v>
@@ -29169,7 +29148,7 @@
         <v>277</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>93</v>
@@ -29181,7 +29160,7 @@
         <v>3.0</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>316</v>
@@ -29202,13 +29181,13 @@
         <v>93</v>
       </c>
       <c r="P94" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q94" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R94" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="Q94" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R94" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S94" s="2" t="s">
         <v>93</v>
@@ -29252,10 +29231,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>95</v>
@@ -29264,7 +29243,7 @@
         <v>278</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>93</v>
@@ -29276,7 +29255,7 @@
         <v>3.0</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>316</v>
@@ -29297,7 +29276,7 @@
         <v>93</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q95" s="2" t="s">
         <v>93</v>
@@ -29347,10 +29326,10 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>594</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>95</v>
@@ -29359,7 +29338,7 @@
         <v>279</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>93</v>
@@ -29371,7 +29350,7 @@
         <v>3.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>316</v>
@@ -29442,10 +29421,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>95</v>
@@ -29466,7 +29445,7 @@
         <v>3.0</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>316</v>
@@ -29487,7 +29466,7 @@
         <v>93</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q97" s="2" t="s">
         <v>93</v>
@@ -29537,19 +29516,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>93</v>
@@ -29632,19 +29611,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>93</v>
@@ -29677,7 +29656,7 @@
         <v>93</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q99" s="2" t="s">
         <v>93</v>
@@ -29727,19 +29706,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>93</v>
@@ -29772,7 +29751,7 @@
         <v>93</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q100" s="2" t="s">
         <v>93</v>
@@ -29784,7 +29763,7 @@
         <v>93</v>
       </c>
       <c r="T100" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U100" s="2" t="n">
         <v>743.0</v>
@@ -29822,10 +29801,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>95</v>
@@ -29834,7 +29813,7 @@
         <v>287</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>93</v>
@@ -29917,10 +29896,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>95</v>
@@ -29941,7 +29920,7 @@
         <v>1.0</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>316</v>
@@ -30012,10 +29991,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>95</v>
@@ -30024,7 +30003,7 @@
         <v>145</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>93</v>
@@ -30036,7 +30015,7 @@
         <v>3.0</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>316</v>
@@ -30057,7 +30036,7 @@
         <v>93</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q103" s="2" t="s">
         <v>93</v>
@@ -30107,10 +30086,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>614</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>95</v>
@@ -30131,7 +30110,7 @@
         <v>2.0</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>316</v>
@@ -30152,7 +30131,7 @@
         <v>93</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q104" s="2" t="s">
         <v>93</v>
@@ -30202,10 +30181,10 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>95</v>
@@ -30214,7 +30193,7 @@
         <v>147</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>93</v>
@@ -30226,7 +30205,7 @@
         <v>1.0</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>316</v>
@@ -30297,10 +30276,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>95</v>
@@ -30321,7 +30300,7 @@
         <v>3.0</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>316</v>
@@ -30342,7 +30321,7 @@
         <v>93</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q106" s="2" t="s">
         <v>93</v>
@@ -30392,19 +30371,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>620</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>93</v>
@@ -30416,7 +30395,7 @@
         <v>2.0</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>316</v>
@@ -30437,7 +30416,7 @@
         <v>93</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q107" s="2" t="s">
         <v>93</v>
@@ -30487,10 +30466,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>95</v>
@@ -30499,10 +30478,10 @@
         <v>151</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>321</v>
@@ -30511,7 +30490,7 @@
         <v>2.0</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>316</v>
@@ -30532,7 +30511,7 @@
         <v>93</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q108" s="2" t="s">
         <v>93</v>
@@ -30582,16 +30561,16 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>329</v>
@@ -30606,7 +30585,7 @@
         <v>3.0</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>316</v>
@@ -30627,7 +30606,7 @@
         <v>93</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q109" s="2" t="s">
         <v>93</v>
@@ -30677,10 +30656,10 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>95</v>
@@ -30689,7 +30668,7 @@
         <v>155</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>93</v>
@@ -30701,7 +30680,7 @@
         <v>2.0</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>316</v>
@@ -30722,7 +30701,7 @@
         <v>93</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q110" s="2" t="s">
         <v>93</v>
@@ -30772,10 +30751,10 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>95</v>
@@ -30784,7 +30763,7 @@
         <v>156</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>93</v>
@@ -30796,7 +30775,7 @@
         <v>1.0</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>316</v>
@@ -30817,7 +30796,7 @@
         <v>93</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q111" s="2" t="s">
         <v>93</v>
@@ -30867,19 +30846,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>93</v>
@@ -30891,7 +30870,7 @@
         <v>2.0</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>316</v>
@@ -30915,10 +30894,10 @@
         <v>93</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="R112" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S112" s="2" t="s">
         <v>93</v>
@@ -30962,19 +30941,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>93</v>
@@ -30986,7 +30965,7 @@
         <v>2.0</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>316</v>
@@ -31007,7 +30986,7 @@
         <v>93</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q113" s="2" t="s">
         <v>93</v>
@@ -31057,19 +31036,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>93</v>
@@ -31081,7 +31060,7 @@
         <v>3.0</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>316</v>
@@ -31102,7 +31081,7 @@
         <v>93</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q114" s="2" t="s">
         <v>93</v>
@@ -31114,7 +31093,7 @@
         <v>93</v>
       </c>
       <c r="T114" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="U114" s="2" t="n">
         <v>387.0</v>
@@ -31152,10 +31131,10 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>95</v>
@@ -31164,7 +31143,7 @@
         <v>163</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>93</v>
@@ -31176,7 +31155,7 @@
         <v>1.0</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>316</v>
@@ -31197,7 +31176,7 @@
         <v>93</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q115" s="2" t="s">
         <v>93</v>
@@ -31247,22 +31226,22 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>314</v>
@@ -31271,7 +31250,7 @@
         <v>2.0</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>316</v>
@@ -31342,10 +31321,10 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>95</v>
@@ -31354,7 +31333,7 @@
         <v>166</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>93</v>
@@ -31366,7 +31345,7 @@
         <v>1.0</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>316</v>
@@ -31387,7 +31366,7 @@
         <v>93</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q117" s="2" t="s">
         <v>93</v>
@@ -31437,19 +31416,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>93</v>
@@ -31494,7 +31473,7 @@
         <v>93</v>
       </c>
       <c r="T118" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="U118" s="2" t="n">
         <v>734.0</v>
@@ -31532,10 +31511,10 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>95</v>
@@ -31544,7 +31523,7 @@
         <v>169</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>93</v>
@@ -31627,10 +31606,10 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>95</v>
@@ -31672,13 +31651,13 @@
         <v>93</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q120" s="2" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="S120" s="2" t="s">
         <v>93</v>
@@ -31722,10 +31701,10 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>95</v>
@@ -31734,7 +31713,7 @@
         <v>171</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>93</v>
@@ -31767,7 +31746,7 @@
         <v>93</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q121" s="2" t="s">
         <v>93</v>
@@ -31817,22 +31796,22 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>312</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>325</v>
@@ -31841,7 +31820,7 @@
         <v>1.0</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>316</v>
@@ -31862,7 +31841,7 @@
         <v>93</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q122" s="2" t="s">
         <v>93</v>
@@ -31912,10 +31891,10 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>95</v>
@@ -31936,7 +31915,7 @@
         <v>3.0</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>316</v>
@@ -32007,10 +31986,10 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>95</v>
@@ -32019,7 +31998,7 @@
         <v>175</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>93</v>
@@ -32031,7 +32010,7 @@
         <v>1.0</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>316</v>
@@ -32052,7 +32031,7 @@
         <v>93</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q124" s="2" t="s">
         <v>93</v>
@@ -32102,10 +32081,10 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>95</v>
@@ -32114,7 +32093,7 @@
         <v>176</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>93</v>
@@ -32126,7 +32105,7 @@
         <v>1.0</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>316</v>
@@ -32197,16 +32176,16 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>312</v>
@@ -32221,7 +32200,7 @@
         <v>2.0</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>316</v>
@@ -32242,7 +32221,7 @@
         <v>93</v>
       </c>
       <c r="P126" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q126" s="2" t="s">
         <v>93</v>
@@ -32292,10 +32271,10 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>95</v>
@@ -32304,7 +32283,7 @@
         <v>180</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>93</v>
@@ -32316,7 +32295,7 @@
         <v>2.0</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>316</v>
@@ -32387,22 +32366,22 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>325</v>
@@ -32411,7 +32390,7 @@
         <v>2.0</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>316</v>
@@ -32432,7 +32411,7 @@
         <v>93</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q128" s="2" t="s">
         <v>93</v>
@@ -32482,10 +32461,10 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>95</v>
@@ -32494,7 +32473,7 @@
         <v>183</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>93</v>
@@ -32506,7 +32485,7 @@
         <v>1.0</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>316</v>
@@ -32577,10 +32556,10 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>95</v>
@@ -32589,7 +32568,7 @@
         <v>184</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>93</v>
@@ -32601,7 +32580,7 @@
         <v>3.0</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>316</v>
@@ -32622,7 +32601,7 @@
         <v>93</v>
       </c>
       <c r="P130" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q130" s="2" t="s">
         <v>93</v>
@@ -32672,19 +32651,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>93</v>
@@ -32696,7 +32675,7 @@
         <v>1.0</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>316</v>
@@ -32714,7 +32693,7 @@
         <v>93</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P131" s="2" t="s">
         <v>93</v>
@@ -32723,7 +32702,7 @@
         <v>93</v>
       </c>
       <c r="R131" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S131" s="2" t="s">
         <v>93</v>
@@ -32767,10 +32746,10 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>95</v>
@@ -32779,10 +32758,10 @@
         <v>187</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>321</v>
@@ -32791,7 +32770,7 @@
         <v>3.0</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>316</v>
@@ -32812,7 +32791,7 @@
         <v>93</v>
       </c>
       <c r="P132" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q132" s="2" t="s">
         <v>93</v>
@@ -32862,10 +32841,10 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>95</v>
@@ -32874,10 +32853,10 @@
         <v>188</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>314</v>
@@ -32886,7 +32865,7 @@
         <v>3.0</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>316</v>
@@ -32907,7 +32886,7 @@
         <v>93</v>
       </c>
       <c r="P133" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q133" s="2" t="s">
         <v>93</v>
@@ -32957,19 +32936,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>93</v>
@@ -32981,7 +32960,7 @@
         <v>3.0</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>316</v>
@@ -33052,10 +33031,10 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>95</v>
@@ -33064,10 +33043,10 @@
         <v>191</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>314</v>
@@ -33076,7 +33055,7 @@
         <v>2.0</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>316</v>
@@ -33097,7 +33076,7 @@
         <v>93</v>
       </c>
       <c r="P135" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q135" s="2" t="s">
         <v>93</v>
@@ -33147,10 +33126,10 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>691</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>95</v>
@@ -33159,7 +33138,7 @@
         <v>192</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>93</v>
@@ -33192,7 +33171,7 @@
         <v>93</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q136" s="2" t="s">
         <v>93</v>
@@ -33242,22 +33221,22 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>314</v>
@@ -33287,7 +33266,7 @@
         <v>93</v>
       </c>
       <c r="P137" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q137" s="2" t="s">
         <v>93</v>
@@ -33337,19 +33316,19 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>93</v>
@@ -33432,19 +33411,19 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D139" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>701</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>93</v>
@@ -33477,7 +33456,7 @@
         <v>93</v>
       </c>
       <c r="P139" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q139" s="2" t="s">
         <v>93</v>
@@ -33527,10 +33506,10 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>703</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>95</v>
@@ -33539,7 +33518,7 @@
         <v>199</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>93</v>
@@ -33572,7 +33551,7 @@
         <v>93</v>
       </c>
       <c r="P140" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q140" s="2" t="s">
         <v>93</v>
@@ -33622,19 +33601,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>93</v>
@@ -33646,7 +33625,7 @@
         <v>3.0</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>316</v>
@@ -33664,7 +33643,7 @@
         <v>93</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P141" s="2" t="s">
         <v>93</v>
@@ -33673,7 +33652,7 @@
         <v>93</v>
       </c>
       <c r="R141" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S141" s="2" t="s">
         <v>93</v>
@@ -33717,10 +33696,10 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>95</v>
@@ -33732,7 +33711,7 @@
         <v>320</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>325</v>
@@ -33741,7 +33720,7 @@
         <v>3.0</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>316</v>
@@ -33762,7 +33741,7 @@
         <v>93</v>
       </c>
       <c r="P142" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q142" s="2" t="s">
         <v>93</v>
@@ -33812,10 +33791,10 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>95</v>
@@ -33824,7 +33803,7 @@
         <v>203</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>93</v>
@@ -33836,7 +33815,7 @@
         <v>2.0</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>316</v>
@@ -33907,10 +33886,10 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>95</v>
@@ -33931,7 +33910,7 @@
         <v>3.0</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>316</v>
@@ -34002,10 +33981,10 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>95</v>
@@ -34014,7 +33993,7 @@
         <v>205</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>93</v>
@@ -34026,7 +34005,7 @@
         <v>3.0</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>316</v>
@@ -34047,7 +34026,7 @@
         <v>93</v>
       </c>
       <c r="P145" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q145" s="2" t="s">
         <v>93</v>
@@ -34097,10 +34076,10 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>715</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>95</v>
@@ -34121,7 +34100,7 @@
         <v>1.0</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>316</v>
@@ -34142,7 +34121,7 @@
         <v>93</v>
       </c>
       <c r="P146" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q146" s="2" t="s">
         <v>93</v>
@@ -34192,10 +34171,10 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>95</v>
@@ -34204,7 +34183,7 @@
         <v>207</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>93</v>
@@ -34216,7 +34195,7 @@
         <v>3.0</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>316</v>
@@ -34237,7 +34216,7 @@
         <v>93</v>
       </c>
       <c r="P147" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q147" s="2" t="s">
         <v>93</v>
@@ -34287,10 +34266,10 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>95</v>
@@ -34299,7 +34278,7 @@
         <v>208</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>93</v>
@@ -34311,7 +34290,7 @@
         <v>2.0</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>316</v>
@@ -34382,10 +34361,10 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>95</v>
@@ -34394,7 +34373,7 @@
         <v>209</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>93</v>
@@ -34406,7 +34385,7 @@
         <v>3.0</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>316</v>
@@ -34477,19 +34456,19 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>93</v>
@@ -34501,7 +34480,7 @@
         <v>1.0</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>316</v>
@@ -34522,7 +34501,7 @@
         <v>93</v>
       </c>
       <c r="P150" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q150" s="2" t="s">
         <v>93</v>
@@ -34572,19 +34551,19 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>93</v>
@@ -34596,7 +34575,7 @@
         <v>1.0</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>316</v>
@@ -34614,7 +34593,7 @@
         <v>93</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P151" s="2" t="s">
         <v>93</v>
@@ -34623,7 +34602,7 @@
         <v>93</v>
       </c>
       <c r="R151" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S151" s="2" t="s">
         <v>93</v>
@@ -34667,10 +34646,10 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>95</v>
@@ -34679,7 +34658,7 @@
         <v>214</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>93</v>
@@ -34691,7 +34670,7 @@
         <v>2.0</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>316</v>
@@ -34712,7 +34691,7 @@
         <v>93</v>
       </c>
       <c r="P152" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q152" s="2" t="s">
         <v>93</v>
@@ -34762,10 +34741,10 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>95</v>
@@ -34786,7 +34765,7 @@
         <v>2.0</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>316</v>
@@ -34816,7 +34795,7 @@
         <v>93</v>
       </c>
       <c r="S153" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T153" s="2" t="s">
         <v>93</v>
@@ -34857,16 +34836,16 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>320</v>
@@ -34881,7 +34860,7 @@
         <v>3.0</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>316</v>
@@ -34952,10 +34931,10 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>95</v>
@@ -34964,7 +34943,7 @@
         <v>218</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>93</v>
@@ -34997,7 +34976,7 @@
         <v>93</v>
       </c>
       <c r="P155" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q155" s="2" t="s">
         <v>93</v>
@@ -35047,10 +35026,10 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>95</v>
@@ -35059,7 +35038,7 @@
         <v>219</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>93</v>
@@ -35142,19 +35121,19 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>739</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D157" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E157" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>93</v>
@@ -35237,10 +35216,10 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>95</v>
@@ -35249,7 +35228,7 @@
         <v>222</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>93</v>
@@ -35282,13 +35261,13 @@
         <v>93</v>
       </c>
       <c r="P158" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q158" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R158" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="Q158" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R158" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S158" s="2" t="s">
         <v>93</v>
@@ -35332,10 +35311,10 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>745</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>95</v>
@@ -35427,10 +35406,10 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>747</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>95</v>
@@ -35439,7 +35418,7 @@
         <v>224</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>93</v>
@@ -35451,7 +35430,7 @@
         <v>2.0</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>316</v>
@@ -35472,7 +35451,7 @@
         <v>93</v>
       </c>
       <c r="P160" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q160" s="2" t="s">
         <v>93</v>
@@ -35522,19 +35501,19 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D161" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>93</v>
@@ -35546,7 +35525,7 @@
         <v>3.0</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>316</v>
@@ -35567,7 +35546,7 @@
         <v>93</v>
       </c>
       <c r="P161" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q161" s="2" t="s">
         <v>93</v>
@@ -35617,10 +35596,10 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>753</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>95</v>
@@ -35629,7 +35608,7 @@
         <v>227</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>93</v>
@@ -35641,7 +35620,7 @@
         <v>3.0</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>316</v>
@@ -35662,7 +35641,7 @@
         <v>93</v>
       </c>
       <c r="P162" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q162" s="2" t="s">
         <v>93</v>
@@ -35712,10 +35691,10 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>95</v>
@@ -35724,7 +35703,7 @@
         <v>228</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>93</v>
@@ -35736,7 +35715,7 @@
         <v>3.0</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>316</v>
@@ -35757,7 +35736,7 @@
         <v>93</v>
       </c>
       <c r="P163" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q163" s="2" t="s">
         <v>93</v>
@@ -35807,10 +35786,10 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>95</v>
@@ -35831,7 +35810,7 @@
         <v>3.0</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>316</v>
@@ -35852,7 +35831,7 @@
         <v>93</v>
       </c>
       <c r="P164" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q164" s="2" t="s">
         <v>93</v>
@@ -35902,19 +35881,19 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>761</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D165" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>93</v>
@@ -35926,7 +35905,7 @@
         <v>2.0</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>316</v>
@@ -35947,7 +35926,7 @@
         <v>93</v>
       </c>
       <c r="P165" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q165" s="2" t="s">
         <v>93</v>
@@ -35997,19 +35976,19 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D166" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>93</v>
@@ -36021,7 +36000,7 @@
         <v>2.0</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>316</v>
@@ -36042,7 +36021,7 @@
         <v>93</v>
       </c>
       <c r="P166" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q166" s="2" t="s">
         <v>93</v>
@@ -36092,10 +36071,10 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>95</v>
@@ -36107,7 +36086,7 @@
         <v>320</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>325</v>
@@ -36116,7 +36095,7 @@
         <v>1.0</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>316</v>
@@ -36137,7 +36116,7 @@
         <v>93</v>
       </c>
       <c r="P167" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q167" s="2" t="s">
         <v>93</v>
@@ -36187,22 +36166,22 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>325</v>
@@ -36211,7 +36190,7 @@
         <v>1.0</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>316</v>
@@ -36232,7 +36211,7 @@
         <v>93</v>
       </c>
       <c r="P168" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q168" s="2" t="s">
         <v>93</v>
@@ -36282,10 +36261,10 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>774</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>95</v>
@@ -36294,7 +36273,7 @@
         <v>238</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>93</v>
@@ -36306,7 +36285,7 @@
         <v>3.0</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>316</v>
@@ -36377,10 +36356,10 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>95</v>
@@ -36401,7 +36380,7 @@
         <v>2.0</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>316</v>
@@ -36472,10 +36451,10 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>95</v>
@@ -36484,7 +36463,7 @@
         <v>240</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>93</v>
@@ -36496,7 +36475,7 @@
         <v>2.0</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>316</v>
@@ -36567,10 +36546,10 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>780</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>95</v>
@@ -36579,10 +36558,10 @@
         <v>241</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>325</v>
@@ -36591,7 +36570,7 @@
         <v>2.0</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>316</v>
@@ -36612,7 +36591,7 @@
         <v>93</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q172" s="2" t="s">
         <v>93</v>
@@ -36662,10 +36641,10 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>95</v>
@@ -36674,7 +36653,7 @@
         <v>242</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>93</v>
@@ -36686,7 +36665,7 @@
         <v>2.0</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>316</v>
@@ -36707,7 +36686,7 @@
         <v>93</v>
       </c>
       <c r="P173" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q173" s="2" t="s">
         <v>93</v>
@@ -36757,16 +36736,16 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>320</v>
@@ -36781,7 +36760,7 @@
         <v>2.0</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>316</v>
@@ -36852,10 +36831,10 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>95</v>
@@ -36864,7 +36843,7 @@
         <v>245</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>93</v>
@@ -36897,7 +36876,7 @@
         <v>93</v>
       </c>
       <c r="P175" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q175" s="2" t="s">
         <v>93</v>
@@ -36947,10 +36926,10 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>95</v>
@@ -36959,7 +36938,7 @@
         <v>246</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>93</v>
@@ -37042,19 +37021,19 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>93</v>
@@ -37137,10 +37116,10 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>95</v>
@@ -37149,7 +37128,7 @@
         <v>251</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>93</v>
@@ -37182,7 +37161,7 @@
         <v>93</v>
       </c>
       <c r="P178" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q178" s="2" t="s">
         <v>93</v>
@@ -37232,10 +37211,10 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>797</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>95</v>
@@ -37256,7 +37235,7 @@
         <v>3.0</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>316</v>
@@ -37277,7 +37256,7 @@
         <v>93</v>
       </c>
       <c r="P179" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q179" s="2" t="s">
         <v>93</v>
@@ -37327,10 +37306,10 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>799</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>95</v>
@@ -37339,10 +37318,10 @@
         <v>253</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>321</v>
@@ -37351,7 +37330,7 @@
         <v>3.0</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>316</v>
@@ -37372,7 +37351,7 @@
         <v>93</v>
       </c>
       <c r="P180" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q180" s="2" t="s">
         <v>93</v>
@@ -37422,19 +37401,19 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>93</v>
@@ -37446,7 +37425,7 @@
         <v>3.0</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>316</v>
@@ -37467,7 +37446,7 @@
         <v>93</v>
       </c>
       <c r="P181" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q181" s="2" t="s">
         <v>93</v>
@@ -37517,10 +37496,10 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>804</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>95</v>
@@ -37529,7 +37508,7 @@
         <v>258</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>93</v>
@@ -37541,7 +37520,7 @@
         <v>1.0</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>316</v>
@@ -37562,7 +37541,7 @@
         <v>93</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q182" s="2" t="s">
         <v>93</v>
@@ -37612,10 +37591,10 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B183" s="2" t="s">
         <v>805</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>806</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>95</v>
@@ -37624,7 +37603,7 @@
         <v>259</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>93</v>
@@ -37636,7 +37615,7 @@
         <v>3.0</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>316</v>
@@ -37707,10 +37686,10 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B184" s="2" t="s">
         <v>807</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>808</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>95</v>
@@ -37719,7 +37698,7 @@
         <v>260</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>93</v>
@@ -37731,7 +37710,7 @@
         <v>3.0</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>316</v>
@@ -37752,7 +37731,7 @@
         <v>93</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q184" s="2" t="s">
         <v>93</v>
@@ -37802,10 +37781,10 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B185" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>810</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>95</v>
@@ -37826,7 +37805,7 @@
         <v>2.0</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>316</v>
@@ -37847,7 +37826,7 @@
         <v>93</v>
       </c>
       <c r="P185" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q185" s="2" t="s">
         <v>93</v>
@@ -37897,10 +37876,10 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B186" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>812</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>95</v>
@@ -37909,7 +37888,7 @@
         <v>262</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>93</v>
@@ -37921,7 +37900,7 @@
         <v>3.0</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>316</v>
@@ -37942,7 +37921,7 @@
         <v>93</v>
       </c>
       <c r="P186" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q186" s="2" t="s">
         <v>93</v>
@@ -37992,16 +37971,16 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>815</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>312</v>
@@ -38016,7 +37995,7 @@
         <v>1.0</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>316</v>
@@ -38037,13 +38016,13 @@
         <v>93</v>
       </c>
       <c r="P187" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q187" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R187" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="Q187" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R187" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S187" s="2" t="s">
         <v>93</v>
@@ -38087,16 +38066,16 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>817</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>818</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>320</v>
@@ -38111,7 +38090,7 @@
         <v>1.0</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>316</v>
@@ -38132,7 +38111,7 @@
         <v>93</v>
       </c>
       <c r="P188" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q188" s="2" t="s">
         <v>93</v>
@@ -38182,22 +38161,22 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B189" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>820</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>314</v>
@@ -38206,7 +38185,7 @@
         <v>3.0</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>316</v>
@@ -38227,7 +38206,7 @@
         <v>93</v>
       </c>
       <c r="P189" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q189" s="2" t="s">
         <v>93</v>
@@ -38277,10 +38256,10 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>822</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>823</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>95</v>
@@ -38289,7 +38268,7 @@
         <v>271</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>93</v>
@@ -38301,7 +38280,7 @@
         <v>3.0</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>316</v>
@@ -38322,7 +38301,7 @@
         <v>93</v>
       </c>
       <c r="P190" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q190" s="2" t="s">
         <v>93</v>
@@ -38372,10 +38351,10 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>95</v>
@@ -38384,7 +38363,7 @@
         <v>272</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>93</v>
@@ -38396,7 +38375,7 @@
         <v>3.0</v>
       </c>
       <c r="I191" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>316</v>
@@ -38467,10 +38446,10 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B192" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>828</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>95</v>
@@ -38479,7 +38458,7 @@
         <v>273</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>93</v>
@@ -38491,7 +38470,7 @@
         <v>1.0</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>316</v>
@@ -38512,7 +38491,7 @@
         <v>93</v>
       </c>
       <c r="P192" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q192" s="2" t="s">
         <v>93</v>
@@ -38562,10 +38541,10 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B193" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>830</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>95</v>
@@ -38574,7 +38553,7 @@
         <v>274</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>93</v>
@@ -38657,10 +38636,10 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B194" s="2" t="s">
         <v>831</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>832</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>95</v>
@@ -38702,7 +38681,7 @@
         <v>93</v>
       </c>
       <c r="P194" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q194" s="2" t="s">
         <v>93</v>
@@ -38752,10 +38731,10 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>833</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>834</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>95</v>
@@ -38794,7 +38773,7 @@
         <v>93</v>
       </c>
       <c r="O195" s="2" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="P195" s="2" t="s">
         <v>93</v>
@@ -38803,7 +38782,7 @@
         <v>93</v>
       </c>
       <c r="R195" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="S195" s="2" t="s">
         <v>93</v>
@@ -38847,19 +38826,19 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>835</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>836</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>93</v>
@@ -38892,7 +38871,7 @@
         <v>93</v>
       </c>
       <c r="P196" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q196" s="2" t="s">
         <v>93</v>
@@ -38942,16 +38921,16 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>838</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>839</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>312</v>
@@ -38987,7 +38966,7 @@
         <v>93</v>
       </c>
       <c r="P197" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q197" s="2" t="s">
         <v>93</v>
@@ -39037,19 +39016,19 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>841</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>842</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>93</v>
@@ -39061,7 +39040,7 @@
         <v>1.0</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>316</v>
@@ -39082,7 +39061,7 @@
         <v>93</v>
       </c>
       <c r="P198" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q198" s="2" t="s">
         <v>93</v>
@@ -39132,10 +39111,10 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>843</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>844</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>95</v>
@@ -39144,7 +39123,7 @@
         <v>283</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>93</v>
@@ -39156,7 +39135,7 @@
         <v>3.0</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>316</v>
@@ -39227,10 +39206,10 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>845</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>846</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>95</v>
@@ -39239,7 +39218,7 @@
         <v>284</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>93</v>
@@ -39251,7 +39230,7 @@
         <v>3.0</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>316</v>
@@ -39272,7 +39251,7 @@
         <v>93</v>
       </c>
       <c r="P200" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q200" s="2" t="s">
         <v>93</v>
@@ -39322,22 +39301,22 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B201" s="2" t="s">
         <v>847</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>848</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>314</v>
@@ -39346,7 +39325,7 @@
         <v>2.0</v>
       </c>
       <c r="I201" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>316</v>
@@ -39417,10 +39396,10 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B202" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>95</v>
@@ -39429,7 +39408,7 @@
         <v>287</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>93</v>
@@ -39441,7 +39420,7 @@
         <v>3.0</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>316</v>
@@ -39512,16 +39491,16 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B203" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>312</v>
@@ -39536,7 +39515,7 @@
         <v>2.0</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>316</v>
@@ -39607,10 +39586,10 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B204" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>855</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>95</v>
@@ -39619,7 +39598,7 @@
         <v>319</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>93</v>
@@ -39631,7 +39610,7 @@
         <v>1.0</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>316</v>
@@ -39652,7 +39631,7 @@
         <v>93</v>
       </c>
       <c r="P204" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q204" s="2" t="s">
         <v>93</v>
@@ -39702,10 +39681,10 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B205" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>95</v>
@@ -39714,10 +39693,10 @@
         <v>148</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>321</v>
@@ -39726,7 +39705,7 @@
         <v>1.0</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>316</v>
@@ -39797,19 +39776,19 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>858</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>859</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>93</v>
@@ -39821,7 +39800,7 @@
         <v>1.0</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>316</v>
@@ -39839,7 +39818,7 @@
         <v>93</v>
       </c>
       <c r="O206" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P206" s="2" t="s">
         <v>93</v>
@@ -39848,7 +39827,7 @@
         <v>93</v>
       </c>
       <c r="R206" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S206" s="2" t="s">
         <v>93</v>
@@ -39892,16 +39871,16 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>861</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>862</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>312</v>
@@ -39916,7 +39895,7 @@
         <v>1.0</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>316</v>
@@ -39937,7 +39916,7 @@
         <v>93</v>
       </c>
       <c r="P207" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q207" s="2" t="s">
         <v>93</v>
@@ -39987,19 +39966,19 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B208" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>864</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>93</v>
@@ -40011,7 +39990,7 @@
         <v>3.0</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>316</v>
@@ -40082,10 +40061,10 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B209" s="2" t="s">
         <v>866</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>867</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>95</v>
@@ -40094,7 +40073,7 @@
         <v>155</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>93</v>
@@ -40106,7 +40085,7 @@
         <v>3.0</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>316</v>
@@ -40177,16 +40156,16 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B210" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>870</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>320</v>
@@ -40201,7 +40180,7 @@
         <v>2.0</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>316</v>
@@ -40222,7 +40201,7 @@
         <v>93</v>
       </c>
       <c r="P210" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="Q210" s="2" t="s">
         <v>93</v>
@@ -40272,10 +40251,10 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B211" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>873</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>95</v>
@@ -40284,7 +40263,7 @@
         <v>158</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>93</v>
@@ -40296,7 +40275,7 @@
         <v>1.0</v>
       </c>
       <c r="I211" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>316</v>
@@ -40317,7 +40296,7 @@
         <v>93</v>
       </c>
       <c r="P211" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q211" s="2" t="s">
         <v>93</v>
@@ -40367,10 +40346,10 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B212" s="2" t="s">
         <v>874</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>875</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>95</v>
@@ -40379,7 +40358,7 @@
         <v>159</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>313</v>
@@ -40412,7 +40391,7 @@
         <v>93</v>
       </c>
       <c r="P212" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q212" s="2" t="s">
         <v>93</v>
@@ -40462,10 +40441,10 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>876</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>877</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>95</v>
@@ -40474,7 +40453,7 @@
         <v>160</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>93</v>
@@ -40507,13 +40486,13 @@
         <v>93</v>
       </c>
       <c r="P213" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q213" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R213" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="Q213" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R213" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S213" s="2" t="s">
         <v>93</v>
@@ -40557,10 +40536,10 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>878</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>879</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>95</v>
@@ -40569,10 +40548,10 @@
         <v>161</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>321</v>
@@ -40652,10 +40631,10 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>880</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>881</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>95</v>
@@ -40747,10 +40726,10 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>882</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>883</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>95</v>
@@ -40762,7 +40741,7 @@
         <v>320</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>321</v>
@@ -40792,7 +40771,7 @@
         <v>93</v>
       </c>
       <c r="P216" s="2" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="Q216" s="2" t="s">
         <v>93</v>
@@ -40842,10 +40821,10 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>884</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>885</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>95</v>
@@ -40854,7 +40833,7 @@
         <v>164</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>93</v>
@@ -40866,7 +40845,7 @@
         <v>3.0</v>
       </c>
       <c r="I217" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>316</v>
@@ -40958,10 +40937,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>886</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="2"/>
@@ -40970,16 +40949,16 @@
         <v>291</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>890</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="4">
@@ -41019,7 +40998,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>216.0</v>
@@ -41214,7 +41193,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -41447,7 +41426,7 @@
         <v>120</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -42504,7 +42483,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -43687,7 +43666,7 @@
         <v>164</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -49763,7 +49742,7 @@
         <v>93</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D125" s="10" t="s">
         <v>93</v>
@@ -49822,7 +49801,7 @@
         <v>93</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>93</v>
@@ -51156,7 +51135,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -51221,7 +51200,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -51274,10 +51253,10 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>93</v>
